--- a/docs/Matriz_Maestra_Contenidos.xlsx
+++ b/docs/Matriz_Maestra_Contenidos.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/04300e833dd7f0dd/DocumentosJES/Singular_AI/Clientes/GS127/Tropa/Libro_Animado_investidura/docs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4DC6D7E-C776-4D61-921D-08A56A6DEA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="1176" yWindow="1308" windowWidth="21600" windowHeight="11232" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Matriz Maestra" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Banco de Preguntas" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Matriz Maestra" sheetId="1" r:id="rId1"/>
+    <sheet name="Banco de Preguntas (120)" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -21,268 +26,1348 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="84">
-  <si>
-    <t xml:space="preserve">Cap.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre del Capítulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requisitos Tabla de Progresión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente Bitácora (tema)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecánica interactiva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insignia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado guion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado arte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado audio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Origen del Fuego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Qué es el Escultismo - Historia | 18. Quién fue B.P. - Historia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biografía B.P., Mafeking, Brownsea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novela visual interactiva + completar biografía</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardián de la Historia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Código del Explorador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Ley Scout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los 10 artículos de la Ley Scout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arrastrar artículo &lt;-&gt; significado + viñetas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardián de la Ley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mi Palabra de Honor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Promesa Scout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promesa Scout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memorización progresiva con huecos crecientes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portador de la Promesa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Raíces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Principios Scouts | 5. Virtudes Scouts | 6. Oración Scout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principios, virtudes, oración</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clasificador de categorías + karaoke de oración</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raíces Firmes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Símbolos de la Hermandad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. Seña Scout | 8. Lema Scout | 9. Flor de Lis | 12. Saludo con la mano izquierda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flor de lis, saludo, seña, lema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flor de lis interactiva + animación de saludo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heraldo de la Flor de Lis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Uniforme del Aventurero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. Uniforme e Insignias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uniforme, pañoleta (colores rojo/amarillo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vestir al scout (drag&amp;drop) + colorear pañoleta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porte Impecable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Buena Acción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11. Historia de la Buena Acción | 13. Nombre y firma Scout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historia de la buena acción</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Animación + diario de buenas acciones (validación)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mano Amiga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Lenguaje de la Tropa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14. Llamados con Silbato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llamados de pito en clave Morse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quiz de audio (escuchar y responder)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oído de Explorador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formaciones y Bordón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15. Formaciones de Tropa | 16. Usos del Bordón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formaciones, usos del bordón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulador táctico de formaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maestro de Formación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mi Tropa, Mi Familia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17. Organigramas de la Tropa y el Grupo | 19. Conocer y pertenecer a una patrulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organigrama, patrulla, lema, grito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constructor de organigrama + editor de ficha de patrulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Espíritu de Patrulla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Prueba del Campista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20. Mínimo 2 noches de Campamento | 4 meses de participación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitácora de campamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registro de noches con código de validación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bajo las Estrellas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Gran Ceremonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rendimiento académico | Comportamiento en el hogar | Repaso general</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceremonia de investidura completa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Examen final integrador (20 preguntas, min. 80%) + animación de ceremonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candidato a Investidura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N° Pregunta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pregunta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opción correcta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distractores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente (pág. Bitácora)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué significa el color ROJO de nuestra pañoleta?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opción múltiple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La fuerza del espíritu que nos fortalece para cumplir las metas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La riqueza del alma y el corazón | El valor y el coraje | La pureza de intención</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué significa el color AMARILLO de nuestra pañoleta?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La riqueza del alma y el corazón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La fuerza del espíritu que nos fortalece para cumplir las metas | La alegría del servicio | El sol que guía el camino</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="445">
+  <si>
+    <t>Cap.</t>
+  </si>
+  <si>
+    <t>Nombre del Capítulo</t>
+  </si>
+  <si>
+    <t>Requisitos Tabla de Progresión</t>
+  </si>
+  <si>
+    <t>Fuente Bitácora (tema)</t>
+  </si>
+  <si>
+    <t>Mecánica interactiva</t>
+  </si>
+  <si>
+    <t>Insignia</t>
+  </si>
+  <si>
+    <t>Estado guion</t>
+  </si>
+  <si>
+    <t>Estado arte</t>
+  </si>
+  <si>
+    <t>Estado audio</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>El Origen del Fuego</t>
+  </si>
+  <si>
+    <t>1. Qué es el Escultismo - Historia | 18. Quién fue B.P. - Historia</t>
+  </si>
+  <si>
+    <t>Biografía B.P., Mafeking, Brownsea</t>
+  </si>
+  <si>
+    <t>Novela visual interactiva + completar biografía</t>
+  </si>
+  <si>
+    <t>Guardián de la Historia</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>El Código del Explorador</t>
+  </si>
+  <si>
+    <t>2. Ley Scout</t>
+  </si>
+  <si>
+    <t>Los 10 artículos de la Ley Scout</t>
+  </si>
+  <si>
+    <t>Arrastrar artículo &lt;-&gt; significado + viñetas</t>
+  </si>
+  <si>
+    <t>Guardián de la Ley</t>
+  </si>
+  <si>
+    <t>Mi Palabra de Honor</t>
+  </si>
+  <si>
+    <t>3. Promesa Scout</t>
+  </si>
+  <si>
+    <t>Promesa Scout</t>
+  </si>
+  <si>
+    <t>Memorización progresiva con huecos crecientes</t>
+  </si>
+  <si>
+    <t>Portador de la Promesa</t>
+  </si>
+  <si>
+    <t>Las Raíces</t>
+  </si>
+  <si>
+    <t>4. Principios Scouts | 5. Virtudes Scouts | 6. Oración Scout</t>
+  </si>
+  <si>
+    <t>Principios, virtudes, oración</t>
+  </si>
+  <si>
+    <t>Clasificador de categorías + karaoke de oración</t>
+  </si>
+  <si>
+    <t>Raíces Firmes</t>
+  </si>
+  <si>
+    <t>Los Símbolos de la Hermandad</t>
+  </si>
+  <si>
+    <t>7. Seña Scout | 8. Lema Scout | 9. Flor de Lis | 12. Saludo con la mano izquierda</t>
+  </si>
+  <si>
+    <t>Flor de lis, saludo, seña, lema</t>
+  </si>
+  <si>
+    <t>Flor de lis interactiva + animación de saludo</t>
+  </si>
+  <si>
+    <t>Heraldo de la Flor de Lis</t>
+  </si>
+  <si>
+    <t>El Uniforme del Aventurero</t>
+  </si>
+  <si>
+    <t>10. Uniforme e Insignias</t>
+  </si>
+  <si>
+    <t>Uniforme, pañoleta (colores rojo/amarillo)</t>
+  </si>
+  <si>
+    <t>Vestir al scout (drag&amp;drop) + colorear pañoleta</t>
+  </si>
+  <si>
+    <t>Porte Impecable</t>
+  </si>
+  <si>
+    <t>La Buena Acción</t>
+  </si>
+  <si>
+    <t>11. Historia de la Buena Acción | 13. Nombre y firma Scout</t>
+  </si>
+  <si>
+    <t>Historia de la buena acción</t>
+  </si>
+  <si>
+    <t>Animación + diario de buenas acciones (validación)</t>
+  </si>
+  <si>
+    <t>Mano Amiga</t>
+  </si>
+  <si>
+    <t>El Lenguaje de la Tropa</t>
+  </si>
+  <si>
+    <t>14. Llamados con Silbato</t>
+  </si>
+  <si>
+    <t>Llamados de pito en clave Morse</t>
+  </si>
+  <si>
+    <t>Quiz de audio (escuchar y responder)</t>
+  </si>
+  <si>
+    <t>Oído de Explorador</t>
+  </si>
+  <si>
+    <t>Formaciones y Bordón</t>
+  </si>
+  <si>
+    <t>15. Formaciones de Tropa | 16. Usos del Bordón</t>
+  </si>
+  <si>
+    <t>Formaciones, usos del bordón</t>
+  </si>
+  <si>
+    <t>Simulador táctico de formaciones</t>
+  </si>
+  <si>
+    <t>Maestro de Formación</t>
+  </si>
+  <si>
+    <t>Mi Tropa, Mi Familia</t>
+  </si>
+  <si>
+    <t>17. Organigramas de la Tropa y el Grupo | 19. Conocer y pertenecer a una patrulla</t>
+  </si>
+  <si>
+    <t>Organigrama, patrulla, lema, grito</t>
+  </si>
+  <si>
+    <t>Constructor de organigrama + editor de ficha de patrulla</t>
+  </si>
+  <si>
+    <t>Espíritu de Patrulla</t>
+  </si>
+  <si>
+    <t>La Prueba del Campista</t>
+  </si>
+  <si>
+    <t>20. Mínimo 2 noches de Campamento | 4 meses de participación</t>
+  </si>
+  <si>
+    <t>Bitácora de campamento</t>
+  </si>
+  <si>
+    <t>Registro de noches con código de validación</t>
+  </si>
+  <si>
+    <t>Bajo las Estrellas</t>
+  </si>
+  <si>
+    <t>La Gran Ceremonia</t>
+  </si>
+  <si>
+    <t>Rendimiento académico | Comportamiento en el hogar | Repaso general</t>
+  </si>
+  <si>
+    <t>Ceremonia de investidura completa</t>
+  </si>
+  <si>
+    <t>Examen final integrador (20 preguntas, min. 80%) + animación de ceremonia</t>
+  </si>
+  <si>
+    <t>Candidato a Investidura</t>
+  </si>
+  <si>
+    <t>Pregunta</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Respuesta correcta / Contenido</t>
+  </si>
+  <si>
+    <t>Distractores</t>
+  </si>
+  <si>
+    <t>Fuente</t>
+  </si>
+  <si>
+    <t>¿En qué año nació Baden Powell?</t>
+  </si>
+  <si>
+    <t>Completar espacio</t>
+  </si>
+  <si>
+    <t>1857</t>
+  </si>
+  <si>
+    <t>1860 | 1852 | 1870</t>
+  </si>
+  <si>
+    <t>Bitácora - Historia del Fundador</t>
+  </si>
+  <si>
+    <t>¿Qué rango militar alcanzó B.P. a los 26 años?</t>
+  </si>
+  <si>
+    <t>Opción múltiple</t>
+  </si>
+  <si>
+    <t>Depende del dato local a confirmar por dirigente</t>
+  </si>
+  <si>
+    <t>Bitácora - Historia del Fundador (espacio en blanco)</t>
+  </si>
+  <si>
+    <t>¿Cómo llamaron los nativos africanos a B.P. por su habilidad para acechar?</t>
+  </si>
+  <si>
+    <t>Lobo que nunca duerme</t>
+  </si>
+  <si>
+    <t>El águila veloz | El tigre silencioso | El guerrero sabio</t>
+  </si>
+  <si>
+    <t>¿Cuántos días duró el sitio de Mafeking que B.P. defendió?</t>
+  </si>
+  <si>
+    <t>217 días</t>
+  </si>
+  <si>
+    <t>100 días | 365 días | 30 días</t>
+  </si>
+  <si>
+    <t>¿En qué isla realizó B.P. el primer campamento experimental en 1907?</t>
+  </si>
+  <si>
+    <t>Isla de Brownsea</t>
+  </si>
+  <si>
+    <t>Isla de Man | Isla de Wight | Isla de Malta</t>
+  </si>
+  <si>
+    <t>¿Cómo se llamó el libro que B.P. publicó en 1908, ilustrado por él mismo?</t>
+  </si>
+  <si>
+    <t>Escultismo para Muchachos</t>
+  </si>
+  <si>
+    <t>Ayudas para el Escultismo | Manual del Explorador | El Camino del Scout</t>
+  </si>
+  <si>
+    <t>¿En qué año fue proclamado B.P. Jefe Scout Mundial, durante el primer Jamboree en Londres?</t>
+  </si>
+  <si>
+    <t>Dato a completar según Bitácora</t>
+  </si>
+  <si>
+    <t>Verdadero o Falso: B.P. era conocido por sus habilidades como actor y como portero de fútbol en su escuela.</t>
+  </si>
+  <si>
+    <t>Verdadero/Falso</t>
+  </si>
+  <si>
+    <t>Verdadero</t>
+  </si>
+  <si>
+    <t>Falso</t>
+  </si>
+  <si>
+    <t>¿Cuál es el significado central de la Divisa Scout, según el legado de B.P.?</t>
+  </si>
+  <si>
+    <t>Hacer una buena acción diaria</t>
+  </si>
+  <si>
+    <t>Ganar todas las competencias | Ser el mejor de la patrulla | Memorizar la Ley Scout</t>
+  </si>
+  <si>
+    <t>Bitácora - Divisa Scout</t>
+  </si>
+  <si>
+    <t>Según el último mensaje de B.P., ¿cuál es la verdadera manera de obtener la felicidad?</t>
+  </si>
+  <si>
+    <t>Haciendo felices a los demás</t>
+  </si>
+  <si>
+    <t>Teniendo éxito en la carrera | Dándose gusto a uno mismo | Acumulando riqueza</t>
+  </si>
+  <si>
+    <t>Bitácora - Último mensaje de B.P.</t>
+  </si>
+  <si>
+    <t>¿Cuál es el artículo 1 de la Ley Scout?</t>
+  </si>
+  <si>
+    <t>Arrastrar/Emparejar</t>
+  </si>
+  <si>
+    <t>El Scout cifra su honor en ser digno de confianza.</t>
+  </si>
+  <si>
+    <t>Los otros 9 artículos como distractores</t>
+  </si>
+  <si>
+    <t>Bitácora - Ley Scout</t>
+  </si>
+  <si>
+    <t>¿Cuál es el artículo 2 de la Ley Scout?</t>
+  </si>
+  <si>
+    <t>El Scout es leal.</t>
+  </si>
+  <si>
+    <t>¿Cuál es el artículo 3 de la Ley Scout?</t>
+  </si>
+  <si>
+    <t>El Scout es útil y ayuda a los demás sin esperar recompensa.</t>
+  </si>
+  <si>
+    <t>¿Cuál es el artículo 4 de la Ley Scout?</t>
+  </si>
+  <si>
+    <t>El Scout es amigo de todos y hermano de cualquier Scout sin distinción de credo, raza, nacionalidad o clase social.</t>
+  </si>
+  <si>
+    <t>¿Cuál es el artículo 5 de la Ley Scout?</t>
+  </si>
+  <si>
+    <t>El Scout es cortés y respeta las convicciones de los demás.</t>
+  </si>
+  <si>
+    <t>¿Cuál es el artículo 6 de la Ley Scout?</t>
+  </si>
+  <si>
+    <t>El Scout ve en la naturaleza la obra de Dios y procura su conservación y progreso.</t>
+  </si>
+  <si>
+    <t>¿Cuál es el artículo 7 de la Ley Scout?</t>
+  </si>
+  <si>
+    <t>El Scout es obediente, responsable y ordenado.</t>
+  </si>
+  <si>
+    <t>¿Cuál es el artículo 8 de la Ley Scout?</t>
+  </si>
+  <si>
+    <t>El Scout sonríe y canta en sus dificultades.</t>
+  </si>
+  <si>
+    <t>¿Cuál es el artículo 9 de la Ley Scout?</t>
+  </si>
+  <si>
+    <t>El Scout es económico, trabajador y cuidadoso del bien ajeno.</t>
+  </si>
+  <si>
+    <t>¿Cuál es el artículo 10 de la Ley Scout?</t>
+  </si>
+  <si>
+    <t>El Scout es limpio y sano, puro en pensamientos, palabras y acciones.</t>
+  </si>
+  <si>
+    <t>¿Ante quién hace el scout su Promesa en la ceremonia de investidura?</t>
+  </si>
+  <si>
+    <t>Ante el resto de la Tropa</t>
+  </si>
+  <si>
+    <t>Solo ante el dirigente | Solo ante su patrulla | Ante sus padres únicamente</t>
+  </si>
+  <si>
+    <t>Bitácora - Promesa Scout</t>
+  </si>
+  <si>
+    <t>Según B.P., la Promesa Scout es...</t>
+  </si>
+  <si>
+    <t>Muy seria y difícil de cumplir, requiere el máximo esfuerzo</t>
+  </si>
+  <si>
+    <t>Solo un formalismo de la ceremonia</t>
+  </si>
+  <si>
+    <t>Recita de memoria la Promesa Scout completa (evaluación oral/escrita con espacios crecientes).</t>
+  </si>
+  <si>
+    <t>Completar espacio (memoria progresiva)</t>
+  </si>
+  <si>
+    <t>Texto oficial de la Promesa de la Asociación Scouts de Colombia</t>
+  </si>
+  <si>
+    <t>Confirmar texto exacto con jefe pedagógico / Escultismo para Muchachos</t>
+  </si>
+  <si>
+    <t>¿Qué representan las tres partes que se prometen por el honor, según el significado del saludo?</t>
+  </si>
+  <si>
+    <t>Cumplir deberes, ayudar al prójimo y cumplir la Ley Scout</t>
+  </si>
+  <si>
+    <t>Ganar insignias, acampar y cantar</t>
+  </si>
+  <si>
+    <t>Bitácora - Saludo Scout (vínculo con la Promesa)</t>
+  </si>
+  <si>
+    <t>Verdadero o Falso: La Promesa se hace solo una vez en la vida scout y nunca más se recuerda.</t>
+  </si>
+  <si>
+    <t>¿Qué se realiza inmediatamente después de la Promesa ante la Tropa?</t>
+  </si>
+  <si>
+    <t>Iniciar los desafíos de la fase de progresión (Vigía)</t>
+  </si>
+  <si>
+    <t>Recibir el rango de Expedicionario directamente</t>
+  </si>
+  <si>
+    <t>Bitácora - Ruta de la Progresión</t>
+  </si>
+  <si>
+    <t>Después de la Promesa ante la Tropa, ¿ante quién se hace la promesa de patrulla?</t>
+  </si>
+  <si>
+    <t>Ante el guía, en compañía de todos los integrantes de la patrulla</t>
+  </si>
+  <si>
+    <t>Ante el Jefe de Grupo en solitario</t>
+  </si>
+  <si>
+    <t>Bitácora - La Patrulla Scout</t>
+  </si>
+  <si>
+    <t>¿Qué actitud debe tener el scout al comprometerse con su Promesa según la Bitácora?</t>
+  </si>
+  <si>
+    <t>Comprender el compromiso con su sociedad, país y familia</t>
+  </si>
+  <si>
+    <t>Solo memorizar el texto sin comprenderlo</t>
+  </si>
+  <si>
+    <t>Bitácora - previo a la investidura</t>
+  </si>
+  <si>
+    <t>¿Qué scout puede solicitar la ceremonia de investidura?</t>
+  </si>
+  <si>
+    <t>El que se siente listo para asumir el nuevo estilo de vida scout</t>
+  </si>
+  <si>
+    <t>Cualquiera sin importar su preparación</t>
+  </si>
+  <si>
+    <t>La palabra de honor en la Promesa Scout se sostiene con:</t>
+  </si>
+  <si>
+    <t>El compromiso personal y la voluntad de cumplirla</t>
+  </si>
+  <si>
+    <t>Solo la supervisión del dirigente</t>
+  </si>
+  <si>
+    <t>¿Cuáles son los tres principios scouts?</t>
+  </si>
+  <si>
+    <t>Clasificar categorías</t>
+  </si>
+  <si>
+    <t>Deberes para con la espiritualidad, deberes para con los demás/las cosas/el medio ambiente, deberes para consigo mismo</t>
+  </si>
+  <si>
+    <t>Virtudes como distractor (Lealtad, Pureza, Abnegación)</t>
+  </si>
+  <si>
+    <t>Bitácora - Principios</t>
+  </si>
+  <si>
+    <t>¿Cuáles son las tres virtudes scouts mencionadas en la Bitácora?</t>
+  </si>
+  <si>
+    <t>Lealtad, Pureza, Abnegación</t>
+  </si>
+  <si>
+    <t>Principios como distractor</t>
+  </si>
+  <si>
+    <t>Bitácora - Virtudes</t>
+  </si>
+  <si>
+    <t>La virtud de la Lealtad está basada en:</t>
+  </si>
+  <si>
+    <t>La verdad y la sinceridad</t>
+  </si>
+  <si>
+    <t>La fuerza y la competencia</t>
+  </si>
+  <si>
+    <t>La virtud de la Abnegación se define como:</t>
+  </si>
+  <si>
+    <t>El sacrificio espontáneo de bienes, voluntad y afectos por el bien del prójimo</t>
+  </si>
+  <si>
+    <t>La capacidad de ganar competencias sin ayuda</t>
+  </si>
+  <si>
+    <t>El principio de 'deberes para con la espiritualidad' implica:</t>
+  </si>
+  <si>
+    <t>La lealtad a la religión propia y la aceptación de sus deberes</t>
+  </si>
+  <si>
+    <t>Ser el más fuerte de la patrulla</t>
+  </si>
+  <si>
+    <t>El principio de 'deberes para con los demás' incluye:</t>
+  </si>
+  <si>
+    <t>Lealtad al país, paz, cooperación y respeto a la dignidad humana</t>
+  </si>
+  <si>
+    <t>Ganar todas las insignias posibles</t>
+  </si>
+  <si>
+    <t>¿Qué pide el scout a Dios en la Oración Scout, según su primera línea?</t>
+  </si>
+  <si>
+    <t>Enséñame a ser generoso</t>
+  </si>
+  <si>
+    <t>Enséñame a ser el mejor | Enséñame a ganar | Enséñame a mandar</t>
+  </si>
+  <si>
+    <t>Bitácora - Oración Scout</t>
+  </si>
+  <si>
+    <t>Ordena las líneas de la Oración Scout (karaoke / secuencia).</t>
+  </si>
+  <si>
+    <t>Ordenar secuencia</t>
+  </si>
+  <si>
+    <t>Secuencia oficial de la Oración Scout de la Bitácora</t>
+  </si>
+  <si>
+    <t>Verdadero o Falso: La virtud de la Pureza se relaciona con ser puro en pensamientos, palabras y acciones.</t>
+  </si>
+  <si>
+    <t>El principio de 'deberes para consigo mismo' se resume en:</t>
+  </si>
+  <si>
+    <t>La responsabilidad en el desarrollo personal</t>
+  </si>
+  <si>
+    <t>La obligación de complacer siempre a los demás</t>
+  </si>
+  <si>
+    <t>¿Cuál es el lema scout?</t>
+  </si>
+  <si>
+    <t>¡Siempre Listo!</t>
+  </si>
+  <si>
+    <t>Siempre Unidos | Adelante Siempre | Fuerza y Honor</t>
+  </si>
+  <si>
+    <t>Bitácora - Lema</t>
+  </si>
+  <si>
+    <t>¿Qué representan los tres dedos (índice, medio, anular) en la seña scout?</t>
+  </si>
+  <si>
+    <t>Los principios y virtudes scout, y las tres partes de la Promesa</t>
+  </si>
+  <si>
+    <t>Las tres patrullas de la tropa</t>
+  </si>
+  <si>
+    <t>Bitácora - Saludo Scout</t>
+  </si>
+  <si>
+    <t>¿Qué significan el pulgar y el meñique unidos en el saludo scout?</t>
+  </si>
+  <si>
+    <t>Que el fuerte protege al débil</t>
+  </si>
+  <si>
+    <t>Que el scout ya hizo su Promesa</t>
+  </si>
+  <si>
+    <t>¿En qué ángulo se hace el saludo scout completo?</t>
+  </si>
+  <si>
+    <t>45 grados</t>
+  </si>
+  <si>
+    <t>90 grados | 30 grados | 180 grados</t>
+  </si>
+  <si>
+    <t>¿En qué ceremonias se usa el saludo medio, a 90 grados?</t>
+  </si>
+  <si>
+    <t>En ceremonias como la Promesa Scout</t>
+  </si>
+  <si>
+    <t>En reuniones informales de patrulla</t>
+  </si>
+  <si>
+    <t>Según una de las historias sobre el origen del saludo con la mano izquierda, ¿por qué se saluda así?</t>
+  </si>
+  <si>
+    <t>Porque los guerreros usaban el escudo en la mano izquierda; saludar así mostraba confianza y desprotección</t>
+  </si>
+  <si>
+    <t>Porque la mano derecha estaba ocupada con el bordón</t>
+  </si>
+  <si>
+    <t>Bitácora - Saludo de mano izquierda</t>
+  </si>
+  <si>
+    <t>¿Para qué se usa la Flor de Lis en mapas y brújulas?</t>
+  </si>
+  <si>
+    <t>Para señalar el norte</t>
+  </si>
+  <si>
+    <t>Para señalar el sur | Para decorar el uniforme | Para representar a la patrulla</t>
+  </si>
+  <si>
+    <t>Bitácora - Flor de Lis</t>
+  </si>
+  <si>
+    <t>¿Por qué se escogió la Flor de Lis como insignia de los Scouts?</t>
+  </si>
+  <si>
+    <t>Porque señala la dirección hacia lo alto y marca el camino del deber</t>
+  </si>
+  <si>
+    <t>Porque era el escudo de armas de B.P.</t>
+  </si>
+  <si>
+    <t>¿Qué se superpone a la Flor de Lis para distinguir cada nacionalidad Scout?</t>
+  </si>
+  <si>
+    <t>El emblema de la nación</t>
+  </si>
+  <si>
+    <t>El nombre del fundador | El escudo de la ciudad</t>
+  </si>
+  <si>
+    <t>Verdadero o Falso: La Flor de Lis es la insignia scout reconocida en casi todos los países del mundo.</t>
+  </si>
+  <si>
+    <t>¿Qué significa el color ROJO de la pañoleta del Grupo 127?</t>
+  </si>
+  <si>
+    <t>La fuerza del espíritu que nos fortalece para cumplir las metas</t>
+  </si>
+  <si>
+    <t>La riqueza del alma y el corazón | El valor y el coraje | La pureza de intención</t>
+  </si>
+  <si>
+    <t>Requisito del Grupo 127 (dato aportado por el usuario)</t>
+  </si>
+  <si>
+    <t>¿Qué significa el color AMARILLO de la pañoleta del Grupo 127?</t>
+  </si>
+  <si>
+    <t>La riqueza del alma y el corazón</t>
+  </si>
+  <si>
+    <t>La fuerza del espíritu que nos fortalece para cumplir las metas | La alegría del servicio | El sol que guía el camino</t>
+  </si>
+  <si>
+    <t>¿Qué elemento identifica al scout de un grupo en particular y es también herramienta en la naturaleza?</t>
+  </si>
+  <si>
+    <t>La pañoleta</t>
+  </si>
+  <si>
+    <t>El bordón | La camisa | El morral</t>
+  </si>
+  <si>
+    <t>Bitácora - Uniforme</t>
+  </si>
+  <si>
+    <t>Según B.P., ¿qué demuestra un scout que no porta bien su uniforme?</t>
+  </si>
+  <si>
+    <t>Que no ha asimilado el verdadero espíritu del Escultismo</t>
+  </si>
+  <si>
+    <t>Que pertenece a otra tropa</t>
+  </si>
+  <si>
+    <t>¿A quién debes preguntarle el significado de los colores de la pañoleta de tu grupo?</t>
+  </si>
+  <si>
+    <t>A tu jefe/dirigente</t>
+  </si>
+  <si>
+    <t>A cualquier scout de otro grupo</t>
+  </si>
+  <si>
+    <t>Bitácora - Pañoleta</t>
+  </si>
+  <si>
+    <t>Arrastra cada insignia al lugar correcto del uniforme (manga, pecho, cuello, gorro).</t>
+  </si>
+  <si>
+    <t>Configuración según uniforme oficial del Grupo 127</t>
+  </si>
+  <si>
+    <t>Por definir con dirigente / uniforme oficial</t>
+  </si>
+  <si>
+    <t>Verdadero o Falso: El uso adecuado del uniforme es un acto de orgullo por pertenecer a la Gran Hermandad Scout.</t>
+  </si>
+  <si>
+    <t>¿Qué uso le daba Baden-Powell a la pañoleta, más allá de identificación?</t>
+  </si>
+  <si>
+    <t>Uso práctico en la naturaleza (por ejemplo, vendaje o protección)</t>
+  </si>
+  <si>
+    <t>Ninguno, era solo decorativa</t>
+  </si>
+  <si>
+    <t>Bitácora - Pañoleta (desafío de investigación)</t>
+  </si>
+  <si>
+    <t>¿Dónde se coloca la insignia de patrulla en el uniforme?</t>
+  </si>
+  <si>
+    <t>Según el estándar del Grupo 127 (a confirmar)</t>
+  </si>
+  <si>
+    <t>Por definir con dirigente</t>
+  </si>
+  <si>
+    <t>La pañoleta se debe colorear siguiendo:</t>
+  </si>
+  <si>
+    <t>Los colores oficiales del Grupo Scout 127</t>
+  </si>
+  <si>
+    <t>Los colores que el scout prefiera</t>
+  </si>
+  <si>
+    <t>¿Cuál es la Divisa Scout?</t>
+  </si>
+  <si>
+    <t>Ser siempre el mejor | Ganar toda competencia | Ayudar solo si te lo piden</t>
+  </si>
+  <si>
+    <t>En la historia de la Buena Acción, ¿de qué ciudad era el Sr. Boyce?</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>Nueva York | Boston | Londres</t>
+  </si>
+  <si>
+    <t>Bitácora - Historia de la Buena Acción</t>
+  </si>
+  <si>
+    <t>¿Por qué el muchacho scout no aceptó la propina del Sr. Boyce?</t>
+  </si>
+  <si>
+    <t>Porque un scout no acepta nada por ayudar a alguien</t>
+  </si>
+  <si>
+    <t>Porque no necesitaba el dinero</t>
+  </si>
+  <si>
+    <t>¿Qué hizo el Sr. Boyce después de conocer el Escultismo gracias al muchacho?</t>
+  </si>
+  <si>
+    <t>Llevó el movimiento scout a su país (Estados Unidos)</t>
+  </si>
+  <si>
+    <t>Se hizo scout en Inglaterra y nunca regresó</t>
+  </si>
+  <si>
+    <t>¿Qué pasó con el muchacho que ayudó al Sr. Boyce?</t>
+  </si>
+  <si>
+    <t>Nadie volvió a saber de él, pero nunca se le olvidó</t>
+  </si>
+  <si>
+    <t>Se hizo famoso y dio conferencias</t>
+  </si>
+  <si>
+    <t>Registra tu buena acción de esta semana en el diario (requiere validación de dirigente o padre).</t>
+  </si>
+  <si>
+    <t>Actividad práctica validada</t>
+  </si>
+  <si>
+    <t>Registro con código de validación</t>
+  </si>
+  <si>
+    <t>Mecánica del app - Diario de Buenas Acciones</t>
+  </si>
+  <si>
+    <t>¿En qué década ocurrió la historia de la Buena Acción con el Sr. Boyce?</t>
+  </si>
+  <si>
+    <t>1900s (finales de otoño de 1909)</t>
+  </si>
+  <si>
+    <t>1950s | 1800s | 1930s</t>
+  </si>
+  <si>
+    <t>¿Qué condición climática de Londres marca el inicio de la historia de la Buena Acción?</t>
+  </si>
+  <si>
+    <t>Una niebla espesa que detuvo el tráfico</t>
+  </si>
+  <si>
+    <t>Una tormenta de nieve</t>
+  </si>
+  <si>
+    <t>¿Cuántos años llevaba fundado el movimiento scout cuando Boyce conoció a B.P.?</t>
+  </si>
+  <si>
+    <t>Dos años</t>
+  </si>
+  <si>
+    <t>Diez años | Veinte años</t>
+  </si>
+  <si>
+    <t>Verdadero o Falso: Tu firma y nombre scout son parte de tu identidad dentro de la Tropa.</t>
+  </si>
+  <si>
+    <t>Tabla de Progresión Personal - Requisito 13</t>
+  </si>
+  <si>
+    <t>Escucha el llamado de pito y selecciona su significado correcto (Llamado general de Tropa).</t>
+  </si>
+  <si>
+    <t>Quiz de audio</t>
+  </si>
+  <si>
+    <t>Reunión general de Tropa</t>
+  </si>
+  <si>
+    <t>Silencio | Alarma | Formación por patrullas</t>
+  </si>
+  <si>
+    <t>Código de llamados del Grupo 127 (a confirmar con dirigente)</t>
+  </si>
+  <si>
+    <t>¿Qué llamado usarías para pedir silencio inmediato en el campamento?</t>
+  </si>
+  <si>
+    <t>Llamado de silencio</t>
+  </si>
+  <si>
+    <t>Llamado de reunión | Llamado de alerta</t>
+  </si>
+  <si>
+    <t>Se te pide que la tropa se forme por patrullas. ¿Qué llamado suena?</t>
+  </si>
+  <si>
+    <t>Quiz de audio (inverso)</t>
+  </si>
+  <si>
+    <t>Llamado de formación por patrullas</t>
+  </si>
+  <si>
+    <t>Llamado de alarma | Llamado de silencio</t>
+  </si>
+  <si>
+    <t>¿Qué instrumento se usa tradicionalmente para dar los llamados en la Tropa?</t>
+  </si>
+  <si>
+    <t>El silbato/pito</t>
+  </si>
+  <si>
+    <t>El tambor | La corneta</t>
+  </si>
+  <si>
+    <t>Bitácora - Llamados con silbato</t>
+  </si>
+  <si>
+    <t>Verdadero o Falso: Cada llamado de pito tiene un significado específico y estandarizado en la tropa.</t>
+  </si>
+  <si>
+    <t>¿Por qué es importante conocer bien los llamados de silbato en actividades al aire libre?</t>
+  </si>
+  <si>
+    <t>Permiten comunicación a distancia sin necesidad de gritar</t>
+  </si>
+  <si>
+    <t>Son solo una tradición sin uso práctico</t>
+  </si>
+  <si>
+    <t>Llamado de auxilio o emergencia: identifica el patrón correcto.</t>
+  </si>
+  <si>
+    <t>Patrón oficial del Grupo 127</t>
+  </si>
+  <si>
+    <t>¿Qué llamado indica el final de una actividad o el momento de recoger?</t>
+  </si>
+  <si>
+    <t>¿Qué debes hacer al escuchar el llamado de 'atención'?</t>
+  </si>
+  <si>
+    <t>Detener lo que haces y prestar atención al dirigente</t>
+  </si>
+  <si>
+    <t>Ignorarlo si estás ocupado</t>
+  </si>
+  <si>
+    <t>Ordena de memoria los 3 llamados de pito más usados en tu tropa.</t>
+  </si>
+  <si>
+    <t>Según código oficial del Grupo 127</t>
+  </si>
+  <si>
+    <t>¿En qué mano se porta siempre el bordón durante las formaciones?</t>
+  </si>
+  <si>
+    <t>En la mano derecha</t>
+  </si>
+  <si>
+    <t>En la mano izquierda | Indistintamente</t>
+  </si>
+  <si>
+    <t>Bitácora - Uso del bordón</t>
+  </si>
+  <si>
+    <t>Describe cómo se realiza el saludo con bordón.</t>
+  </si>
+  <si>
+    <t>Bordón cerca del cuerpo en mano derecha, seña scout con la mano izquierda cruzando el pecho</t>
+  </si>
+  <si>
+    <t>Bordón levantado con ambas manos</t>
+  </si>
+  <si>
+    <t>Bitácora - Saludo con bordón</t>
+  </si>
+  <si>
+    <t>En posición de 'siempre listo', ¿cómo deben estar las manos?</t>
+  </si>
+  <si>
+    <t>Empuñadas con los dedos hacia atrás, pegadas al cuerpo</t>
+  </si>
+  <si>
+    <t>Sueltas a los lados</t>
+  </si>
+  <si>
+    <t>Bitácora - Posiciones de formación</t>
+  </si>
+  <si>
+    <t>¿En qué ángulo deben estar los pies en la posición de formación, para dar estabilidad?</t>
+  </si>
+  <si>
+    <t>45 grados con los talones juntos</t>
+  </si>
+  <si>
+    <t>90 grados | Paralelos completamente</t>
+  </si>
+  <si>
+    <t>Observa la señal del dirigente y ubica a tu patrulla en la formación correcta (fila).</t>
+  </si>
+  <si>
+    <t>Simulador visual</t>
+  </si>
+  <si>
+    <t>Formación en fila según señal</t>
+  </si>
+  <si>
+    <t>Mecánica del app - Simulador de formaciones</t>
+  </si>
+  <si>
+    <t>Observa la señal del dirigente y ubica a tu patrulla en la formación correcta (herradura).</t>
+  </si>
+  <si>
+    <t>Formación en herradura según señal</t>
+  </si>
+  <si>
+    <t>Observa la señal del dirigente y ubica a tu patrulla en la formación correcta (círculo).</t>
+  </si>
+  <si>
+    <t>Formación en círculo según señal</t>
+  </si>
+  <si>
+    <t>Verdadero o Falso: El bordón solo tiene uso decorativo y no cumple función práctica en la Tropa.</t>
+  </si>
+  <si>
+    <t>¿Qué uso práctico puede tener el bordón, además de las formaciones?</t>
+  </si>
+  <si>
+    <t>Apoyo para caminar, medir distancias, o armar refugios</t>
+  </si>
+  <si>
+    <t>Ninguno adicional</t>
+  </si>
+  <si>
+    <t>Bitácora - Usos del bordón (desafíos de pionerismo)</t>
+  </si>
+  <si>
+    <t>¿Qué se debe respetar al recibir una señal de formación del dirigente?</t>
+  </si>
+  <si>
+    <t>Ejecutar la formación indicada con orden y rapidez</t>
+  </si>
+  <si>
+    <t>Esperar a que otros se muevan primero</t>
+  </si>
+  <si>
+    <t>Bitácora - Formaciones de Tropa</t>
+  </si>
+  <si>
+    <t>¿Cuántos integrantes suele tener una patrulla scout?</t>
+  </si>
+  <si>
+    <t>Entre seis y ocho</t>
+  </si>
+  <si>
+    <t>Dos o tres | Quince o más</t>
+  </si>
+  <si>
+    <t>¿Qué elige cada patrulla para representarse, según B.P.?</t>
+  </si>
+  <si>
+    <t>El nombre de un animal real y propio de la región</t>
+  </si>
+  <si>
+    <t>Un color únicamente</t>
+  </si>
+  <si>
+    <t>¿Qué es el 'grito de patrulla'?</t>
+  </si>
+  <si>
+    <t>Una frase que resalta las características del animal y de los scouts de la patrulla</t>
+  </si>
+  <si>
+    <t>El nombre oficial de la tropa</t>
+  </si>
+  <si>
+    <t>Arrastra los nombres reales de tu tropa/grupo a su cargo correspondiente en el organigrama.</t>
+  </si>
+  <si>
+    <t>Constructor de organigrama</t>
+  </si>
+  <si>
+    <t>Organigrama real del Grupo 127 (a completar con datos actuales)</t>
+  </si>
+  <si>
+    <t>Bitácora - Organigrama / dato local</t>
+  </si>
+  <si>
+    <t>¿Qué se debe hacer con el banderín de la patrulla?</t>
+  </si>
+  <si>
+    <t>Diseñarlo y dibujarlo como parte de la identidad de la patrulla</t>
+  </si>
+  <si>
+    <t>Ignorarlo, no es obligatorio</t>
+  </si>
+  <si>
+    <t>¿De qué depende el éxito de una patrulla, según la Bitácora?</t>
+  </si>
+  <si>
+    <t>El trabajo en equipo y el cumplimiento responsable de las funciones de cada integrante</t>
+  </si>
+  <si>
+    <t>Tener el integrante más fuerte</t>
+  </si>
+  <si>
+    <t>Verdadero o Falso: Cada patrulla puede tener también un 'llamado de patrulla' que imita el sonido de su animal.</t>
+  </si>
+  <si>
+    <t>¿A quién se le hace la promesa de patrulla, después de la Promesa Scout ante la Tropa?</t>
+  </si>
+  <si>
+    <t>Al guía de patrulla, en compañía de todos los integrantes</t>
+  </si>
+  <si>
+    <t>Al Jefe de Grupo, en privado</t>
+  </si>
+  <si>
+    <t>¿Cuál es tu patrulla dentro del Grupo 127? (selección de identidad de usuario)</t>
+  </si>
+  <si>
+    <t>Selección personal</t>
+  </si>
+  <si>
+    <t>Jaguares / Lobos / Mapaches / Pandas</t>
+  </si>
+  <si>
+    <t>Estructura del Grupo 127</t>
+  </si>
+  <si>
+    <t>Completa la ficha de tu patrulla: lema, grito y datos de tus compañeros.</t>
+  </si>
+  <si>
+    <t>Actividad práctica</t>
+  </si>
+  <si>
+    <t>Ficha completa validada</t>
+  </si>
+  <si>
+    <t>Bitácora - Ficha de patrulla</t>
+  </si>
+  <si>
+    <t>¿Cuántas noches de campamento como mínimo se requieren para la investidura?</t>
+  </si>
+  <si>
+    <t>2 noches</t>
+  </si>
+  <si>
+    <t>1 noche | 5 noches | 10 noches</t>
+  </si>
+  <si>
+    <t>Tabla de Progresión Personal - Requisito 20</t>
+  </si>
+  <si>
+    <t>¿Cuántos meses mínimos de participación se requieren antes de la investidura?</t>
+  </si>
+  <si>
+    <t>4 meses</t>
+  </si>
+  <si>
+    <t>1 mes | 12 meses | 2 meses</t>
+  </si>
+  <si>
+    <t>Registra tu primera noche de campamento (requiere código de validación del dirigente).</t>
+  </si>
+  <si>
+    <t>Código de validación ingresado</t>
+  </si>
+  <si>
+    <t>Mecánica del app - Bitácora de campamento</t>
+  </si>
+  <si>
+    <t>¿Qué filosofía de campismo de bajo impacto recomienda el último mensaje de B.P.?</t>
+  </si>
+  <si>
+    <t>'No deje signos de que se ha estado alguna vez en el lugar'</t>
+  </si>
+  <si>
+    <t>Dejar todo como recuerdo del paso por el lugar</t>
+  </si>
+  <si>
+    <t>Bitácora - Último mensaje de B.P. / campismo de bajo impacto</t>
+  </si>
+  <si>
+    <t>¿Para cuántas personas se recomienda planificar una salida de campamento, según la Bitácora?</t>
+  </si>
+  <si>
+    <t>10 a 12 personas o menos</t>
+  </si>
+  <si>
+    <t>30 personas o más</t>
+  </si>
+  <si>
+    <t>Bitácora - Planificación de una salida</t>
+  </si>
+  <si>
+    <t>Verdadero o Falso: La participación activa y constante en la Tropa es un requisito para la investidura.</t>
+  </si>
+  <si>
+    <t>¿Qué debe incluir la planificación de un campamento según la Bitácora?</t>
+  </si>
+  <si>
+    <t>Ubicación de tiendas, letrinas, baños, hoyos de desperdicios y construcciones básicas</t>
+  </si>
+  <si>
+    <t>Solo el lugar para dormir</t>
+  </si>
+  <si>
+    <t>Bitácora - Planificación de campamento</t>
+  </si>
+  <si>
+    <t>Contador visual: ¿cuántos meses llevas participando activamente en la tropa?</t>
+  </si>
+  <si>
+    <t>Actividad de seguimiento</t>
+  </si>
+  <si>
+    <t>Contador automático desde el registro de ingreso</t>
+  </si>
+  <si>
+    <t>Mecánica del app - Contador de participación</t>
+  </si>
+  <si>
+    <t>¿Qué se recomienda evitar dejar tras un campamento de bajo impacto?</t>
+  </si>
+  <si>
+    <t>Basura, huellas de fogatas mal apagadas, daño a la vegetación</t>
+  </si>
+  <si>
+    <t>Fotografías del lugar</t>
+  </si>
+  <si>
+    <t>Bitácora - Campismo de bajo impacto</t>
+  </si>
+  <si>
+    <t>¿Qué figura valida oficialmente tus noches de campamento en el app?</t>
+  </si>
+  <si>
+    <t>Tu dirigente, mediante un código de validación</t>
+  </si>
+  <si>
+    <t>Cualquier otro scout de tu patrulla</t>
+  </si>
+  <si>
+    <t>Antes de solicitar tu investidura, ¿en qué dos aspectos debes destacarte, según la Bitácora?</t>
+  </si>
+  <si>
+    <t>Rendimiento académico y comportamiento ejemplar en casa</t>
+  </si>
+  <si>
+    <t>Solo en actividades deportivas</t>
+  </si>
+  <si>
+    <t>¿A quién debes buscar cuando te sientas listo para tu ceremonia de investidura?</t>
+  </si>
+  <si>
+    <t>A tu dirigente, para solicitarle la ceremonia</t>
+  </si>
+  <si>
+    <t>A cualquier scout mayor</t>
+  </si>
+  <si>
+    <t>Repaso: ¿Cuál es el lema scout?</t>
+  </si>
+  <si>
+    <t>Repite de Cap. 5</t>
+  </si>
+  <si>
+    <t>Repaso: ¿Qué significa el color ROJO de la pañoleta del Grupo 127?</t>
+  </si>
+  <si>
+    <t>Repite de Cap. 6</t>
+  </si>
+  <si>
+    <t>Requisito del Grupo 127</t>
+  </si>
+  <si>
+    <t>Repaso: ¿Qué significa el color AMARILLO de la pañoleta del Grupo 127?</t>
+  </si>
+  <si>
+    <t>Repaso: ¿Cuál es la Divisa Scout?</t>
+  </si>
+  <si>
+    <t>Repite de Cap. 7</t>
+  </si>
+  <si>
+    <t>Repaso: Nombra los tres principios scouts.</t>
+  </si>
+  <si>
+    <t>Deberes con la espiritualidad, con los demás/cosas/entorno, y consigo mismo</t>
+  </si>
+  <si>
+    <t>Repite de Cap. 4</t>
+  </si>
+  <si>
+    <t>Repaso: ¿Qué representa la Flor de Lis?</t>
+  </si>
+  <si>
+    <t>La dirección hacia lo alto y el camino del deber</t>
+  </si>
+  <si>
+    <t>Validación de comportamiento en el hogar (código de padres).</t>
+  </si>
+  <si>
+    <t>Validación externa</t>
+  </si>
+  <si>
+    <t>Código ingresado por los padres</t>
+  </si>
+  <si>
+    <t>Mecánica del app - Validación de hogar</t>
+  </si>
+  <si>
+    <t>Validación de rendimiento académico (código de dirigente/acudiente).</t>
+  </si>
+  <si>
+    <t>Código ingresado por dirigente</t>
+  </si>
+  <si>
+    <t>Mecánica del app - Validación académica</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,36 +1376,19 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,16 +1401,22 @@
         <bgColor rgb="FF008000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -358,61 +1432,26 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -433,7 +1472,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFFFF3CD"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -471,47 +1510,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -519,12 +1574,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -553,7 +1608,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -574,7 +1629,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -625,7 +1680,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -643,33 +1698,32 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,8 +1755,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -731,8 +1785,8 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -761,8 +1815,8 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -791,8 +1845,8 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -821,8 +1875,8 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -851,8 +1905,8 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -881,8 +1935,8 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -911,8 +1965,8 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -941,8 +1995,8 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -971,8 +2025,8 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1001,8 +2055,8 @@
       </c>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1031,8 +2085,8 @@
       </c>
       <c r="J12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+    <row r="13" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1062,105 +2116,2406 @@
       <c r="J13" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F121"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
+    <col min="6" max="6" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="C2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>2</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>2</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>2</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>2</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>2</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>3</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>3</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <v>3</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>3</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>3</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>3</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>3</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>3</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>3</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>3</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>4</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>4</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>4</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>4</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>4</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>4</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>4</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>4</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>4</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>4</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>5</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>5</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>5</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>5</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>5</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>5</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>5</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>5</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>5</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>5</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="B52" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" s="4"/>
+      <c r="B53" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>6</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>6</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>6</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <v>6</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>6</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>6</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
+        <v>6</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>6</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>7</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>7</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>7</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>7</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>7</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>7</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>7</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>7</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>7</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>7</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3">
+        <v>8</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="3">
+        <v>8</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3">
+        <v>8</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>8</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>8</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>8</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3">
+        <v>8</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="3">
+        <v>8</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>8</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="3">
+        <v>8</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>9</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>9</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>9</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>9</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>9</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>9</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>9</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>9</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>9</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>9</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>10</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>10</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>10</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="3">
+        <v>10</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>10</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>10</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>10</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>10</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>10</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>10</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>11</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>11</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>11</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>11</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>11</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>11</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>11</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>11</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>11</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>11</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>12</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>12</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>12</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>12</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>12</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>12</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>12</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>12</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>12</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>12</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2" t="s">
+        <v>444</v>
+      </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>